--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WISCONSIN_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/WISCONSIN_2018.xlsx
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C633">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C660">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C666">
